--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19190F34-0CF3-4890-8F5E-B43FBAEA7049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C09C45C-DCC2-40BF-8387-E561806C7A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -75,9 +75,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/li_yan_wen.png</t>
-  </si>
-  <si>
     <t>002</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -87,10 +84,6 @@
   </si>
   <si>
     <t>李言闻</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/li_shi_zhen.png</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -245,6 +238,12 @@
   <si>
     <t>哇，太好了！</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
   </si>
 </sst>
 </file>
@@ -303,7 +302,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -313,6 +312,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -373,11 +378,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -668,7 +688,7 @@
     <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.25" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="87.5" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
@@ -699,38 +719,38 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:8" s="16" customFormat="1">
+      <c r="A2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="13">
+        <v>1</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -738,51 +758,51 @@
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>17</v>
+      <c r="E3" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="16" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="13">
+        <v>3</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
+      <c r="G4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>13</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -790,17 +810,17 @@
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>17</v>
+      <c r="E5" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C09C45C-DCC2-40BF-8387-E561806C7A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CF898D-65DF-418B-8A67-783EBB18F51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -135,7 +135,7 @@
   </si>
   <si>
     <r>
-      <t>平常日子里看您治病，其</t>
+      <t>学医最要</t>
     </r>
     <r>
       <rPr>
@@ -145,7 +145,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>实</t>
+      <t>紧</t>
     </r>
     <r>
       <rPr>
@@ -155,7 +155,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>已</t>
+      <t>的是</t>
     </r>
     <r>
       <rPr>
@@ -165,13 +165,70 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>经窥探得些门道了。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>学医最要</t>
+      <t>积</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>累，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吃完晚饭去把这些天教你的内容再看一遍，明日一早你随我一起出诊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哇，太好了！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>嗯，都明白了，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>平常日子里看您治病，其</t>
     </r>
     <r>
       <rPr>
@@ -181,7 +238,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>紧</t>
+      <t>实</t>
     </r>
     <r>
       <rPr>
@@ -191,7 +248,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>的是</t>
+      <t>已</t>
     </r>
     <r>
       <rPr>
@@ -201,56 +258,16 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>积</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>累，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>吃完晚饭去把这些天教你的内容再看一遍，明日一早你随我一起出诊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哇，太好了！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
+      <t>经窥探得些门道了。</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +318,20 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -349,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -398,6 +429,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -739,7 +773,7 @@
         <v>10</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>14</v>
@@ -765,10 +799,10 @@
         <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="16" customFormat="1">
@@ -791,10 +825,10 @@
         <v>10</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -817,10 +851,10 @@
         <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CF898D-65DF-418B-8A67-783EBB18F51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EB2E52-3216-4B03-828D-0A98B7968614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1778" yWindow="1778" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
   <si>
     <t>StoryID</t>
   </si>
@@ -204,12 +193,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-  </si>
-  <si>
-    <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -261,17 +244,25 @@
       <t>经窥探得些门道了。</t>
     </r>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BackgroundPath</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/clinic/autumn.png</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -285,7 +276,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -332,8 +323,15 @@
       <family val="3"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -343,12 +341,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -409,33 +401,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -713,21 +690,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="87.5" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="87.46484375" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -750,36 +728,40 @@
         <v>4</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="16" customFormat="1">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:9">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -792,46 +774,44 @@
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="16" customFormat="1">
-      <c r="A4" s="11" t="s">
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="13" t="s">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
@@ -844,20 +824,19 @@
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="5"/>
       <c r="B6" s="7"/>
       <c r="C6" s="1"/>
@@ -865,9 +844,10 @@
       <c r="E6" s="1"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6" s="2"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="3"/>
@@ -876,8 +856,9 @@
       <c r="F7" s="2"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="3"/>
@@ -886,8 +867,9 @@
       <c r="F8" s="2"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="3"/>
@@ -896,8 +878,9 @@
       <c r="F9" s="2"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="3"/>
@@ -906,8 +889,9 @@
       <c r="F10" s="2"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="3"/>
@@ -916,8 +900,9 @@
       <c r="F11" s="2"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="3"/>
@@ -926,8 +911,9 @@
       <c r="F12" s="2"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="3"/>
@@ -936,6 +922,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EB2E52-3216-4B03-828D-0A98B7968614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B52A69-9E8C-4361-AEF5-2BF4327741BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1778" yWindow="1778" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>StoryID</t>
   </si>
@@ -193,6 +204,14 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>BackgroundPath</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>来了来了。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -201,7 +220,7 @@
         <family val="3"/>
         <charset val="136"/>
       </rPr>
-      <t>嗯，都明白了，</t>
+      <t>都明白了，</t>
     </r>
     <r>
       <rPr>
@@ -241,17 +260,67 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>经窥探得些门道了。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>BackgroundPath</t>
+      <t>经窥得些门道了。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>相公，晚饭做好了，该吃饭了。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>吴芷兰</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>002</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>002</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.png</t>
+    </r>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>res://Assets/Background/clinic/autumn.png</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <t>麻桂相须，增强发汗散寒之力，专治表实无汗。麻杏相使，宣降相配，专治寒邪闭肺之喘逆…</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -262,7 +331,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -276,7 +345,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -325,7 +394,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -372,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -410,9 +479,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -693,15 +765,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="87.46484375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="87.5" style="4" customWidth="1"/>
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -728,13 +800,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="18.75">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -747,18 +819,18 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
+      <c r="E2" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -775,15 +847,15 @@
         <v>6</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="12" t="s">
-        <v>18</v>
+      <c r="I3" s="13" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -799,16 +871,16 @@
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
+      <c r="E4" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="1" t="s">
-        <v>16</v>
+      <c r="I4" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -824,50 +896,92 @@
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>15</v>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="1" t="s">
-        <v>17</v>
+      <c r="I5" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="5"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2"/>
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="12" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="2"/>
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="I7" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2"/>
+      <c r="A8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6"/>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B52A69-9E8C-4361-AEF5-2BF4327741BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61ED0428-DDA4-4263-84DD-9919EDEC8540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="3150" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -273,54 +262,12 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>res://Assets/Background/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>002</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>002</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.png</t>
-    </r>
+    <t>麻桂相须，增强发汗散寒之力，专治表实无汗。麻杏相使，宣降相配，专治寒邪闭肺之喘逆…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/002/002.png</t>
     <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>麻桂相须，增强发汗散寒之力，专治表实无汗。麻杏相使，宣降相配，专治寒邪闭肺之喘逆…</t>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -331,7 +278,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -345,7 +292,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -394,7 +341,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -484,7 +431,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -765,15 +712,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="87.5" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="87.46484375" style="4" customWidth="1"/>
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -806,7 +753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18.75">
+    <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -827,10 +774,10 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="13" t="s">
         <v>23</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:9">

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61ED0428-DDA4-4263-84DD-9919EDEC8540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3095426E-4268-4F4E-9C34-A396617A40BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3090" yWindow="3150" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -119,10 +130,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>李东壁</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <t>学医最要</t>
     </r>
@@ -268,6 +275,9 @@
   <si>
     <t>res://Assets/Background/002/002.png</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>李东璧</t>
   </si>
 </sst>
 </file>
@@ -278,7 +288,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -292,7 +302,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -341,7 +351,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -431,7 +441,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -712,15 +722,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="87.46484375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="87.5" style="4" customWidth="1"/>
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -747,13 +757,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="18.75">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -767,17 +777,17 @@
         <v>6</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -794,7 +804,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -802,7 +812,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -819,7 +829,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>9</v>
@@ -827,7 +837,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -869,7 +879,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>9</v>
@@ -877,7 +887,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -902,7 +912,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -919,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>9</v>
@@ -927,7 +937,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9">

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3095426E-4268-4F4E-9C34-A396617A40BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF57D88-19D4-4AEE-A3B4-1E5208E6D509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="26">
   <si>
     <t>StoryID</t>
   </si>
@@ -278,6 +278,10 @@
   </si>
   <si>
     <t>李东璧</t>
+  </si>
+  <si>
+    <t>Hide</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -398,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -438,6 +442,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -719,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
@@ -729,12 +736,13 @@
     <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="87.5" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="4"/>
+    <col min="8" max="8" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="87.5" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -756,14 +764,17 @@
       <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18.75">
+    <row r="2" spans="1:10" ht="18.75">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -783,14 +794,15 @@
         <v>9</v>
       </c>
       <c r="G2" s="2"/>
-      <c r="H2" t="s">
+      <c r="H2" s="14"/>
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="J2" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -811,11 +823,12 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
@@ -836,11 +849,12 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
@@ -861,11 +875,12 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -886,11 +901,12 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="2"/>
+      <c r="J6" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
@@ -911,11 +927,12 @@
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="3"/>
+      <c r="J7" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -936,11 +953,12 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="3"/>
+      <c r="J8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="3"/>
@@ -950,8 +968,9 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="3"/>
@@ -961,8 +980,9 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="3"/>
@@ -972,8 +992,9 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="3"/>
@@ -983,8 +1004,9 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="3"/>
@@ -994,6 +1016,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,42 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF57D88-19D4-4AEE-A3B4-1E5208E6D509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8582BB-7E0B-4983-9B72-3EA988B003E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Story" sheetId="3" r:id="rId1"/>
+    <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>StoryID</t>
   </si>
@@ -59,27 +49,88 @@
     <t>dialogue</t>
   </si>
   <si>
+    <t>PortraitSide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>left</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BackgroundPath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>StoryName</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>PortraitSide</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>left</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>right</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>002</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>初学医术</t>
+  </si>
+  <si>
+    <t>TriggerType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerScene</t>
+  </si>
+  <si>
+    <t>TriggerDay</t>
+  </si>
+  <si>
+    <t>Reputation</t>
+  </si>
+  <si>
+    <t>EntryId</t>
+  </si>
+  <si>
+    <t>NpcID</t>
+  </si>
+  <si>
+    <t>TriggerNpcID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayOnce</t>
+  </si>
+  <si>
+    <t>ReturnScene</t>
+  </si>
+  <si>
+    <t>SortIndex</t>
+  </si>
+  <si>
+    <t>scene_enter</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>night</t>
+  </si>
+  <si>
+    <t>李东璧</t>
+  </si>
+  <si>
+    <t>res://Assets/Background/002/002.png</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻桂相须，增强发汗散寒之力，专治表实无汗。麻杏相使，宣降相配，专治寒邪闭肺之喘逆…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>吴芷兰</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>相公，晚饭做好了，该吃饭了。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>来了来了。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -131,7 +182,24 @@
   </si>
   <si>
     <r>
-      <t>学医最要</t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>都明白了，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>平常日子里看您治病，其</t>
     </r>
     <r>
       <rPr>
@@ -141,7 +209,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>紧</t>
+      <t>实</t>
     </r>
     <r>
       <rPr>
@@ -151,7 +219,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>的是</t>
+      <t>已</t>
     </r>
     <r>
       <rPr>
@@ -161,7 +229,23 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>积</t>
+      <t>经窥得些门道了。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>学医最要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紧</t>
     </r>
     <r>
       <rPr>
@@ -171,6 +255,26 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>的是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>积</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>累，</t>
     </r>
     <r>
@@ -200,88 +304,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>BackgroundPath</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>来了来了。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>都明白了，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>平常日子里看您治病，其</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>实</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>已</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>经窥得些门道了。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>相公，晚饭做好了，该吃饭了。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>吴芷兰</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>麻桂相须，增强发汗散寒之力，专治表实无汗。麻杏相使，宣降相配，专治寒邪闭肺之喘逆…</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/002/002.png</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>李东璧</t>
-  </si>
-  <si>
-    <t>Hide</t>
-    <phoneticPr fontId="2"/>
+    <t>002</t>
+  </si>
+  <si>
+    <t>初学医术</t>
   </si>
 </sst>
 </file>
@@ -292,7 +318,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -306,7 +332,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -326,11 +352,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -342,9 +368,9 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="3"/>
-      <charset val="136"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -354,14 +380,14 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="游ゴシック"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
       <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <charset val="136"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,6 +397,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -419,36 +457,41 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -725,298 +768,293 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.59765625" customWidth="1"/>
+    <col min="11" max="11" width="13.53125" customWidth="1"/>
+    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="18">
+      <c r="A2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18">
+      <c r="C3" s="11"/>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="1:12" ht="18">
+      <c r="C4" s="11"/>
+    </row>
+    <row r="5" spans="1:12" ht="18">
+      <c r="C5" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="43.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="87.5" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.9296875" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="14"/>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.75">
-      <c r="A2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="14"/>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="C8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="H8" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8582BB-7E0B-4983-9B72-3EA988B003E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6365DDFB-76A0-4AC8-BE48-994324690FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
   <si>
     <t>StoryID</t>
   </si>
@@ -308,6 +319,10 @@
   </si>
   <si>
     <t>初学医术</t>
+  </si>
+  <si>
+    <t>dim</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -318,7 +333,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -332,7 +347,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -353,7 +368,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -477,9 +492,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -489,9 +501,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -770,23 +785,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" customWidth="1"/>
-    <col min="11" max="11" width="13.53125" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18">
+    <row r="1" spans="1:12">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -824,7 +839,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18">
+    <row r="2" spans="1:12">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
@@ -856,14 +871,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18">
+    <row r="3" spans="1:12">
       <c r="C3" s="11"/>
       <c r="J3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="18">
+    <row r="4" spans="1:12">
       <c r="C4" s="11"/>
     </row>
-    <row r="5" spans="1:12" ht="18">
+    <row r="5" spans="1:12">
       <c r="C5" s="11"/>
     </row>
   </sheetData>
@@ -877,14 +892,14 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.9296875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -914,7 +929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="18.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -928,11 +943,13 @@
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="14"/>
+      <c r="F2" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="14" t="s">
         <v>27</v>
       </c>
     </row>
@@ -950,9 +967,11 @@
         <v>9</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="F3" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="G3" s="2"/>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -970,7 +989,9 @@
         <v>8</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="13" t="s">
         <v>30</v>
@@ -990,9 +1011,11 @@
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="15" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1010,9 +1033,11 @@
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1030,7 +1055,9 @@
         <v>9</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="1" t="s">
         <v>34</v>
@@ -1050,7 +1077,9 @@
         <v>8</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="17" t="s">
+        <v>38</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="1" t="s">
         <v>35</v>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6365DDFB-76A0-4AC8-BE48-994324690FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA7CC12-DF99-4960-8CF5-EDD858B67210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
   <si>
     <t>StoryID</t>
   </si>
@@ -323,17 +312,20 @@
   <si>
     <t>dim</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -347,7 +339,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -368,7 +360,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -400,6 +392,14 @@
       <name val="Microsoft JhengHei"/>
       <family val="3"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -481,8 +481,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -504,9 +502,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -784,24 +784,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -814,32 +815,35 @@
       <c r="D1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="17" t="s">
         <v>19</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
@@ -861,25 +865,26 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="b">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="C3" s="11"/>
-      <c r="J3" s="12"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="C4" s="11"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="C5" s="11"/>
+    <row r="3" spans="1:13" ht="18">
+      <c r="C3" s="9"/>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:13" ht="18">
+      <c r="C4" s="9"/>
+    </row>
+    <row r="5" spans="1:13" ht="18">
+      <c r="C5" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -892,14 +897,14 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -929,27 +934,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="12" t="s">
         <v>27</v>
       </c>
     </row>
@@ -960,18 +965,18 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G3" s="2"/>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="12" t="s">
         <v>29</v>
       </c>
     </row>
@@ -982,18 +987,18 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="11" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1011,11 +1016,11 @@
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="13" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1026,18 +1031,18 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1055,7 +1060,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G7" s="3"/>
@@ -1070,14 +1075,14 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="15" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="3"/>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA7CC12-DF99-4960-8CF5-EDD858B67210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2076904D-5935-4B8E-8913-FC0C495719FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2355" yWindow="2475" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
   <si>
     <t>StoryID</t>
   </si>
@@ -325,7 +336,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -339,7 +350,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -360,7 +371,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -506,7 +517,7 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -785,24 +796,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:13">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -843,7 +854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:13">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
@@ -876,14 +887,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:13">
       <c r="C3" s="9"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="1:13" ht="18">
+    <row r="4" spans="1:13">
       <c r="C4" s="9"/>
     </row>
-    <row r="5" spans="1:13" ht="18">
+    <row r="5" spans="1:13">
       <c r="C5" s="9"/>
     </row>
   </sheetData>
@@ -897,14 +908,14 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -934,7 +945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="18.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1002,7 +1013,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="18.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1019,7 +1030,9 @@
       <c r="F5" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
       <c r="H5" s="13" t="s">
         <v>32</v>
       </c>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2076904D-5935-4B8E-8913-FC0C495719FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8755F3AC-9470-4721-96E1-68BC5E67AA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="2475" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
   <si>
     <t>StoryID</t>
   </si>
@@ -326,6 +326,32 @@
   </si>
   <si>
     <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/clinic/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>spring_night</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -963,7 +989,7 @@
         <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>27</v>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8755F3AC-9470-4721-96E1-68BC5E67AA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C128D1-51D6-484D-8337-AF9B8C997568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
   <si>
     <t>StoryID</t>
   </si>
@@ -351,6 +351,10 @@
       </rPr>
       <t>.png</t>
     </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerStoryID</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -358,7 +362,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -541,6 +545,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -821,8 +828,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
@@ -830,16 +837,17 @@
     <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -859,28 +867,31 @@
         <v>16</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="J1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
@@ -899,29 +910,78 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="b">
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C3" s="9"/>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="G3" s="18"/>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C5" s="9"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G20" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -932,7 +992,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
@@ -945,7 +1005,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -971,7 +1031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75">
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -995,7 +1055,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1017,7 +1077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1039,7 +1099,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75">
+    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1063,7 +1123,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1085,7 +1145,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1107,7 +1167,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C128D1-51D6-484D-8337-AF9B8C997568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA48572-5EDE-4927-BECF-B72FB412136B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -831,20 +831,19 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA48572-5EDE-4927-BECF-B72FB412136B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF667C8D-305B-4F9F-BF4E-261FD49A6EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
   <si>
     <t>StoryID</t>
   </si>
@@ -355,6 +355,10 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -443,7 +447,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,6 +469,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -496,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -546,6 +556,12 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -828,25 +844,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -859,38 +876,41 @@
       <c r="D1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="20" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
@@ -903,84 +923,85 @@
       <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1"/>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="1" t="b">
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C3" s="9"/>
-      <c r="G3" s="18"/>
-      <c r="L3" s="10"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="H3" s="18"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C4" s="9"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="H4" s="18"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C5" s="9"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G20" s="18"/>
+      <c r="H5" s="18"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H6" s="18"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H7" s="18"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H8" s="18"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H14" s="18"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H16" s="18"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H20" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF667C8D-305B-4F9F-BF4E-261FD49A6EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF58FC6-1174-40C5-9423-E8E9A1BEF852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="3525" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="45">
   <si>
     <t>StoryID</t>
   </si>
@@ -91,12 +80,6 @@
   </si>
   <si>
     <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>EntryId</t>
   </si>
   <si>
     <t>NpcID</t>
@@ -345,7 +328,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -360,17 +343,33 @@
   <si>
     <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -384,7 +383,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -405,7 +404,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -566,7 +565,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -844,26 +843,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -877,54 +878,60 @@
         <v>14</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="K1" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="17" t="s">
+      <c r="O1" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="P1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="N1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="20" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -938,69 +945,71 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1" t="b">
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17">
       <c r="C3" s="9"/>
       <c r="H3" s="18"/>
-      <c r="N3" s="10"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="C4" s="9"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17">
       <c r="C5" s="9"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17">
       <c r="H16" s="18"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="18"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="18"/>
     </row>
   </sheetData>
@@ -1012,20 +1021,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1051,7 +1060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1059,23 +1068,23 @@
         <v>6</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" t="s">
-        <v>40</v>
-      </c>
       <c r="H2" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1083,21 +1092,21 @@
         <v>6</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1105,21 +1114,21 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1127,23 +1136,23 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1151,21 +1160,21 @@
         <v>6</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1173,21 +1182,21 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1195,18 +1204,18 @@
         <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF58FC6-1174-40C5-9423-E8E9A1BEF852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CA9EBA-F022-479F-ABE6-D7C851B62ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="3525" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -328,7 +339,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -338,10 +349,6 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -365,11 +372,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -383,7 +390,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -404,7 +411,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -565,7 +572,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -843,28 +850,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -884,13 +890,13 @@
         <v>15</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H1" s="16" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>16</v>
@@ -898,26 +904,23 @@
       <c r="K1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>40</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>37</v>
       </c>
       <c r="N1" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="O1" s="19" t="s">
-        <v>42</v>
+      <c r="O1" s="20" t="s">
+        <v>18</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q1" s="20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>34</v>
       </c>
@@ -946,70 +949,69 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="b">
+      <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="P2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="9"/>
       <c r="H3" s="18"/>
-      <c r="P3" s="10"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="9"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="9"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="18"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="18"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="18"/>
     </row>
   </sheetData>
@@ -1021,20 +1023,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1060,7 +1062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1084,7 +1086,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1106,7 +1108,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1128,7 +1130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1152,7 +1154,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1174,7 +1176,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1196,7 +1198,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CA9EBA-F022-479F-ABE6-D7C851B62ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D98371F-1474-4BE0-9948-160597E42578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5317" yWindow="3863" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -96,10 +85,6 @@
     <t>NpcID</t>
   </si>
   <si>
-    <t>TriggerNpcID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
@@ -339,7 +324,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -366,17 +351,21 @@
   <si>
     <t>TriggerEntryId</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -390,7 +379,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -411,7 +400,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -572,7 +561,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -851,26 +840,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -884,57 +873,57 @@
         <v>14</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>43</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>16</v>
       </c>
       <c r="K1" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>18</v>
-      </c>
       <c r="P1" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75">
+      <c r="A2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -956,62 +945,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="9"/>
       <c r="H3" s="18"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="9"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="9"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="18"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="18"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="18"/>
     </row>
   </sheetData>
@@ -1023,20 +1012,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1062,7 +1051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1070,23 +1059,23 @@
         <v>6</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1094,21 +1083,21 @@
         <v>6</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1116,21 +1105,21 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1138,23 +1127,23 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1162,21 +1151,21 @@
         <v>6</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1184,21 +1173,21 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1206,18 +1195,18 @@
         <v>6</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D98371F-1474-4BE0-9948-160597E42578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B7EB62-2D46-4D3C-B6D2-5EB09708CC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5317" yWindow="3863" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18.75">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
         <v>33</v>
       </c>
@@ -928,9 +928,7 @@
       <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="5"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -950,54 +948,54 @@
       <c r="H3" s="18"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16">
       <c r="C4" s="9"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16">
       <c r="C5" s="9"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16">
       <c r="H16" s="18"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="18"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="18"/>
     </row>
     <row r="20" spans="8:8">

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B7EB62-2D46-4D3C-B6D2-5EB09708CC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2F7292-8FDC-4CEA-B750-004C3BBDF84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t>StoryID</t>
   </si>
@@ -128,6 +139,26 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>都明白了，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>平常日子里看您治病，其</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -136,7 +167,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>东</t>
+      <t>实</t>
     </r>
     <r>
       <rPr>
@@ -146,7 +177,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>壁啊，白天教你的都听明白了</t>
+      <t>已</t>
     </r>
     <r>
       <rPr>
@@ -156,7 +187,23 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>吗</t>
+      <t>经窥得些门道了。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>学医最要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紧</t>
     </r>
     <r>
       <rPr>
@@ -166,20 +213,17 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>都明白了，</t>
+      <t>的是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>积</t>
     </r>
     <r>
       <rPr>
@@ -189,8 +233,94 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>平常日子里看您治病，其</t>
-    </r>
+      <t>累，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吃完晚饭去把这些天教你的内容再看一遍，明日一早你随我一起出诊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哇，太好了！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>初学医术</t>
+  </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/clinic/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>spring_night</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -199,7 +329,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>实</t>
+      <t>东璧</t>
     </r>
     <r>
       <rPr>
@@ -209,7 +339,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>已</t>
+      <t>啊，白天教你的都听明白了</t>
     </r>
     <r>
       <rPr>
@@ -219,23 +349,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>经窥得些门道了。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>学医最要</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>紧</t>
+      <t>吗</t>
     </r>
     <r>
       <rPr>
@@ -245,127 +359,20 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>的是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>积</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>累，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>吃完晚饭去把这些天教你的内容再看一遍，明日一早你随我一起出诊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哇，太好了！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>初学医术</t>
-  </si>
-  <si>
-    <t>dim</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <r>
-      <t>res://Assets/Background/clinic/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>spring_night</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.png</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+      <t>？</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -379,7 +386,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -400,7 +407,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -561,7 +568,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -840,26 +847,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -879,28 +886,28 @@
         <v>15</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>16</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>17</v>
@@ -909,12 +916,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>20</v>
@@ -943,62 +950,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="9"/>
       <c r="H3" s="18"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="9"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="9"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="18"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="18"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="18"/>
     </row>
   </sheetData>
@@ -1010,20 +1017,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1049,7 +1056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1063,17 +1070,15 @@
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="15"/>
+      <c r="G2" t="s">
         <v>35</v>
-      </c>
-      <c r="G2" t="s">
-        <v>37</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1087,15 +1092,13 @@
         <v>9</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="F3" s="15"/>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1109,15 +1112,13 @@
         <v>8</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="F4" s="15"/>
       <c r="G4" s="2"/>
       <c r="H4" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1131,17 +1132,15 @@
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="F5" s="15"/>
       <c r="G5" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1155,15 +1154,13 @@
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="F6" s="15"/>
       <c r="G6" s="2"/>
       <c r="H6" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1177,15 +1174,13 @@
         <v>9</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="F7" s="15"/>
       <c r="G7" s="3"/>
       <c r="H7" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1199,12 +1194,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="F8" s="15"/>
       <c r="G8" s="3"/>
       <c r="H8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2F7292-8FDC-4CEA-B750-004C3BBDF84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FC119C-FCE9-44DE-9518-2198300241AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -288,7 +277,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -368,11 +357,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -386,7 +375,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -407,7 +396,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -568,7 +557,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -847,26 +836,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -916,7 +905,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="18.75">
       <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
@@ -950,62 +939,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="9"/>
       <c r="H3" s="18"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="9"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="9"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="18"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="18"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="18"/>
     </row>
   </sheetData>
@@ -1017,20 +1006,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1056,7 +1045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1078,7 +1067,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1098,7 +1087,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1118,7 +1107,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1140,7 +1129,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1160,7 +1149,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1180,7 +1169,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FC119C-FCE9-44DE-9518-2198300241AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAF3BC6-3FA1-4194-86DB-C22C94C96F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -277,7 +288,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -350,6 +361,10 @@
       </rPr>
       <t>？</t>
     </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -357,11 +372,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -375,7 +390,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -396,7 +411,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -557,7 +572,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -836,26 +851,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -905,7 +920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18.75">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
@@ -939,62 +954,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="9"/>
       <c r="H3" s="18"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="9"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="9"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="18"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="18"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="18"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="18"/>
     </row>
   </sheetData>
@@ -1006,20 +1021,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1045,7 +1060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1055,8 +1070,8 @@
       <c r="C2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
+      <c r="D2" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="15"/>
@@ -1067,7 +1082,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1087,7 +1102,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1097,8 +1112,8 @@
       <c r="C4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
+      <c r="D4" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="15"/>
@@ -1107,7 +1122,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1117,8 +1132,8 @@
       <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
+      <c r="D5" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="15"/>
@@ -1129,7 +1144,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1139,7 +1154,7 @@
       <c r="C6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="15" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
@@ -1149,7 +1164,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1159,8 +1174,8 @@
       <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
+      <c r="D7" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="15"/>
@@ -1169,7 +1184,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1179,7 +1194,7 @@
       <c r="C8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="15" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3"/>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAF3BC6-3FA1-4194-86DB-C22C94C96F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9BDACA-7D12-4E4D-8633-1F680758BFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>StoryID</t>
   </si>
@@ -365,6 +365,13 @@
   </si>
   <si>
     <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>一年后…</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1020,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -1065,24 +1072,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>43</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="2"/>
       <c r="F2" s="15"/>
       <c r="G2" t="s">
         <v>35</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1090,16 +1093,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="15"/>
-      <c r="G3" s="2"/>
+      <c r="G3"/>
       <c r="H3" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1110,58 +1113,58 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="15"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="H4" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
+      <c r="C5" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>43</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="15"/>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G5" s="2"/>
+      <c r="H5" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>22</v>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="15"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="14" t="s">
-        <v>29</v>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1171,17 +1174,17 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>28</v>
+      <c r="C7" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="15"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="1" t="s">
-        <v>30</v>
+      <c r="G7" s="2"/>
+      <c r="H7" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1191,16 +1194,36 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>22</v>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="15"/>
       <c r="G8" s="3"/>
       <c r="H8" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="1" t="s">
         <v>31</v>
       </c>
     </row>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9BDACA-7D12-4E4D-8633-1F680758BFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A66B9C-E1F4-4E43-82AB-44685BA54BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>LineIndex</t>
   </si>
@@ -80,33 +66,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
-  </si>
-  <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>night</t>
@@ -268,9 +231,6 @@
     <t>初学医术</t>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
     <r>
       <t>res://Assets/Background/clinic/</t>
     </r>
@@ -288,36 +248,12 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>.png</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -373,17 +309,102 @@
   <si>
     <t>一年后…</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="11"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -397,7 +418,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -418,7 +439,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -454,13 +475,27 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,20 +510,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -519,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -542,9 +579,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -566,20 +600,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -857,170 +911,199 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="18" customFormat="1">
+      <c r="A1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="18" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="D2" s="12">
         <v>1</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1" t="b">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="16"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="9"/>
-      <c r="H3" s="18"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="9"/>
-      <c r="H4" s="18"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="9"/>
-      <c r="H5" s="18"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H6" s="18"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H7" s="18"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="18"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="18"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="18"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="18"/>
+      <c r="T2" s="17"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8"/>
+      <c r="H3" s="15"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:20" ht="18.75">
+      <c r="C4" s="8"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:20" ht="18.75">
+      <c r="C5" s="8"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.75">
+      <c r="H6" s="15"/>
+    </row>
+    <row r="7" spans="1:20" ht="18.75">
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:20" ht="18.75">
+      <c r="H8" s="15"/>
+    </row>
+    <row r="9" spans="1:20" ht="18.75">
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" spans="1:20" ht="18.75">
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:20" ht="18.75">
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:20" ht="18.75">
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="1:20" ht="18.75">
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:20" ht="18.75">
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:20" ht="18.75">
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:20" ht="18.75">
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="8:8" ht="18.75">
+      <c r="H17" s="15"/>
+    </row>
+    <row r="18" spans="8:8" ht="18.75">
+      <c r="H18" s="15"/>
+    </row>
+    <row r="19" spans="8:8" ht="18.75">
+      <c r="H19" s="15"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{9D25CCA6-1E7C-469F-B320-EDC66E900FA4}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{F44EC2B9-1B58-4D99-814F-05C28F84EF20}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{06D1A2B8-E582-4B86-AF9B-EA5A3A3B9E56}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{F9E69A16-859D-41AB-B2C7-44574248C145}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{20720604-09CE-4BB7-A9AC-D7EF8AD4B73B}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1028,203 +1111,203 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="15"/>
+      <c r="F2" s="14"/>
       <c r="G2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>43</v>
+        <v>5</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="15"/>
+      <c r="F3" s="14"/>
       <c r="G3"/>
-      <c r="H3" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H3" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>25</v>
+        <v>5</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="15"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H4" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>43</v>
+        <v>5</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="15"/>
+      <c r="F5" s="14"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="H5" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="15" t="s">
-        <v>43</v>
-      </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="15"/>
+      <c r="F6" s="14"/>
       <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="15"/>
+      <c r="F7" s="14"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H7" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>43</v>
-      </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="15"/>
+      <c r="F8" s="14"/>
       <c r="G8" s="3"/>
       <c r="H8" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="15"/>
+      <c r="F9" s="14"/>
       <c r="G9" s="3"/>
       <c r="H9" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/002初学医术.xlsx
+++ b/DataTables/DetailText/剧情/002初学医术.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A66B9C-E1F4-4E43-82AB-44685BA54BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637BF69B-6AA1-4E5A-A0D9-CA89D4E936CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19395" yWindow="5745" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>LineIndex</t>
   </si>
@@ -248,7 +259,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -393,6 +404,10 @@
   </si>
   <si>
     <t>奖励心得</t>
+    <phoneticPr fontId="11"/>
+  </si>
+  <si>
+    <t>Music</t>
     <phoneticPr fontId="11"/>
   </si>
 </sst>
@@ -404,7 +419,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -418,7 +433,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -439,7 +454,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -556,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -631,9 +646,12 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -912,26 +930,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="18" customFormat="1">
+    <row r="1" spans="1:20" s="18" customFormat="1" ht="18">
       <c r="A1" s="19" t="s">
         <v>31</v>
       </c>
@@ -993,7 +1011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="18" customFormat="1">
+    <row r="2" spans="1:20" s="18" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
@@ -1032,54 +1050,54 @@
       <c r="H3" s="15"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:20" ht="18.75">
+    <row r="4" spans="1:20">
       <c r="C4" s="8"/>
       <c r="H4" s="15"/>
     </row>
-    <row r="5" spans="1:20" ht="18.75">
+    <row r="5" spans="1:20">
       <c r="C5" s="8"/>
       <c r="H5" s="15"/>
     </row>
-    <row r="6" spans="1:20" ht="18.75">
+    <row r="6" spans="1:20">
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:20" ht="18.75">
+    <row r="7" spans="1:20">
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:20" ht="18.75">
+    <row r="8" spans="1:20">
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:20" ht="18.75">
+    <row r="9" spans="1:20">
       <c r="H9" s="15"/>
     </row>
-    <row r="10" spans="1:20" ht="18.75">
+    <row r="10" spans="1:20">
       <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:20" ht="18.75">
+    <row r="11" spans="1:20">
       <c r="H11" s="15"/>
     </row>
-    <row r="12" spans="1:20" ht="18.75">
+    <row r="12" spans="1:20">
       <c r="H12" s="15"/>
     </row>
-    <row r="13" spans="1:20" ht="18.75">
+    <row r="13" spans="1:20">
       <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:20" ht="18.75">
+    <row r="14" spans="1:20">
       <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:20" ht="18.75">
+    <row r="15" spans="1:20">
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:20" ht="18.75">
+    <row r="16" spans="1:20">
       <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="15"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="15"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="15"/>
     </row>
     <row r="20" spans="8:8">
@@ -1110,21 +1128,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1149,8 +1167,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="18.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1167,8 +1188,9 @@
       <c r="H2" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1187,8 +1209,9 @@
       <c r="H3" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1207,8 +1230,9 @@
       <c r="H4" s="11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1227,8 +1251,9 @@
       <c r="H5" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="18.75">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1249,8 +1274,9 @@
       <c r="H6" s="12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1269,8 +1295,9 @@
       <c r="H7" s="13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1289,8 +1316,9 @@
       <c r="H8" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1309,6 +1337,7 @@
       <c r="H9" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="I9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
